--- a/BVSimulationFiles/90.xlsx
+++ b/BVSimulationFiles/90.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00050390625</v>
+        <v>0.0010078125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000518905691501465</v>
+        <v>0.00103781138300293</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005337916159955035</v>
+        <v>0.001067583231991007</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000548564642822741</v>
+        <v>0.001097129285645482</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0005632253883484896</v>
+        <v>0.001126450776696979</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0005777744659760985</v>
+        <v>0.001155548931952197</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0005922124861602463</v>
+        <v>0.001184424972320493</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006065400564201775</v>
+        <v>0.001213080112840355</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00062075778135288</v>
+        <v>0.00124151556270576</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0006348662626462087</v>
+        <v>0.001269732525292417</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006488660990919507</v>
+        <v>0.001297732198183901</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0006627578865988328</v>
+        <v>0.001325515773197666</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0006765422182054782</v>
+        <v>0.001353084436410956</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0006902196840933018</v>
+        <v>0.001380439368186604</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007037908715993534</v>
+        <v>0.001407581743198707</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007172563652291042</v>
+        <v>0.001434512730458208</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007306167466691788</v>
+        <v>0.001461233493338358</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007438725948000326</v>
+        <v>0.001487745189600065</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000757024485708573</v>
+        <v>0.001514048971417146</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0007700729927007298</v>
+        <v>0.00154014598540146</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00050390625</v>
+        <v>0.0010078125</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000518905691501465</v>
+        <v>0.00103781138300293</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005337916159955035</v>
+        <v>0.001067583231991007</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000548564642822741</v>
+        <v>0.001097129285645482</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005632253883484896</v>
+        <v>0.001126450776696979</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005777744659760985</v>
+        <v>0.001155548931952197</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005922124861602463</v>
+        <v>0.001184424972320493</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006065400564201775</v>
+        <v>0.001213080112840355</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00062075778135288</v>
+        <v>0.00124151556270576</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006348662626462087</v>
+        <v>0.001269732525292417</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006488660990919507</v>
+        <v>0.001297732198183901</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006627578865988328</v>
+        <v>0.001325515773197666</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0006765422182054782</v>
+        <v>0.001353084436410956</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0006902196840933018</v>
+        <v>0.001380439368186604</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007037908715993534</v>
+        <v>0.001407581743198707</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007172563652291042</v>
+        <v>0.001434512730458208</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007306167466691788</v>
+        <v>0.001461233493338358</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007438725948000326</v>
+        <v>0.001487745189600065</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000757024485708573</v>
+        <v>0.001514048971417146</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0007700729927007298</v>
+        <v>0.00154014598540146</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/90.xlsx
+++ b/BVSimulationFiles/90.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0010078125</v>
+        <v>0.010078125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00103781138300293</v>
+        <v>0.0103781138300293</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001067583231991007</v>
+        <v>0.01067583231991007</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001097129285645482</v>
+        <v>0.01097129285645482</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001126450776696979</v>
+        <v>0.01126450776696979</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001155548931952197</v>
+        <v>0.01155548931952197</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001184424972320493</v>
+        <v>0.01184424972320493</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001213080112840355</v>
+        <v>0.01213080112840355</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00124151556270576</v>
+        <v>0.0124151556270576</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001269732525292417</v>
+        <v>0.01269732525292417</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001297732198183901</v>
+        <v>0.01297732198183901</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001325515773197666</v>
+        <v>0.01325515773197666</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001353084436410956</v>
+        <v>0.01353084436410956</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001380439368186604</v>
+        <v>0.01380439368186604</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001407581743198707</v>
+        <v>0.01407581743198707</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001434512730458208</v>
+        <v>0.01434512730458208</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001461233493338358</v>
+        <v>0.01461233493338358</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001487745189600065</v>
+        <v>0.01487745189600065</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001514048971417146</v>
+        <v>0.01514048971417146</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00154014598540146</v>
+        <v>0.0154014598540146</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0010078125</v>
+        <v>0.010078125</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00103781138300293</v>
+        <v>0.0103781138300293</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001067583231991007</v>
+        <v>0.01067583231991007</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001097129285645482</v>
+        <v>0.01097129285645482</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001126450776696979</v>
+        <v>0.01126450776696979</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001155548931952197</v>
+        <v>0.01155548931952197</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001184424972320493</v>
+        <v>0.01184424972320493</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001213080112840355</v>
+        <v>0.01213080112840355</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00124151556270576</v>
+        <v>0.0124151556270576</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001269732525292417</v>
+        <v>0.01269732525292417</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001297732198183901</v>
+        <v>0.01297732198183901</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001325515773197666</v>
+        <v>0.01325515773197666</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001353084436410956</v>
+        <v>0.01353084436410956</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001380439368186604</v>
+        <v>0.01380439368186604</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001407581743198707</v>
+        <v>0.01407581743198707</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001434512730458208</v>
+        <v>0.01434512730458208</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001461233493338358</v>
+        <v>0.01461233493338358</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001487745189600065</v>
+        <v>0.01487745189600065</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001514048971417146</v>
+        <v>0.01514048971417146</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00154014598540146</v>
+        <v>0.0154014598540146</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/90.xlsx
+++ b/BVSimulationFiles/90.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,60 +421,90 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.003716842105263158</v>
+        <v>0.002435172413793104</v>
       </c>
       <c r="D1" t="n">
-        <v>0.007433684210526315</v>
+        <v>0.004870344827586207</v>
       </c>
       <c r="E1" t="n">
-        <v>0.01115052631578947</v>
+        <v>0.007305517241379312</v>
       </c>
       <c r="F1" t="n">
-        <v>0.01486736842105263</v>
+        <v>0.009740689655172415</v>
       </c>
       <c r="G1" t="n">
-        <v>0.01858421052631579</v>
+        <v>0.01217586206896552</v>
       </c>
       <c r="H1" t="n">
-        <v>0.02230105263157895</v>
+        <v>0.01461103448275862</v>
       </c>
       <c r="I1" t="n">
-        <v>0.02601789473684211</v>
+        <v>0.01704620689655173</v>
       </c>
       <c r="J1" t="n">
-        <v>0.02973473684210526</v>
+        <v>0.01948137931034483</v>
       </c>
       <c r="K1" t="n">
-        <v>0.03345157894736842</v>
+        <v>0.02191655172413793</v>
       </c>
       <c r="L1" t="n">
-        <v>0.03716842105263158</v>
+        <v>0.02435172413793103</v>
       </c>
       <c r="M1" t="n">
-        <v>0.04088526315789474</v>
+        <v>0.02678689655172414</v>
       </c>
       <c r="N1" t="n">
-        <v>0.04460210526315789</v>
+        <v>0.02922206896551725</v>
       </c>
       <c r="O1" t="n">
-        <v>0.04831894736842104</v>
+        <v>0.03165724137931034</v>
       </c>
       <c r="P1" t="n">
-        <v>0.05203578947368422</v>
+        <v>0.03409241379310345</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.05575263157894737</v>
+        <v>0.03652758620689655</v>
       </c>
       <c r="R1" t="n">
-        <v>0.05946947368421052</v>
+        <v>0.03896275862068966</v>
       </c>
       <c r="S1" t="n">
-        <v>0.06318631578947369</v>
+        <v>0.04139793103448276</v>
       </c>
       <c r="T1" t="n">
-        <v>0.06690315789473683</v>
+        <v>0.04383310344827587</v>
       </c>
       <c r="U1" t="n">
+        <v>0.04626827586206897</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0.04870344827586207</v>
+      </c>
+      <c r="W1" t="n">
+        <v>0.05113862068965518</v>
+      </c>
+      <c r="X1" t="n">
+        <v>0.05357379310344828</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>0.05600896551724138</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>0.05844413793103449</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.06087931034482759</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>0.06331448275862069</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>0.0657496551724138</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>0.06818482758620691</v>
+      </c>
+      <c r="AE1" t="n">
         <v>0.07062</v>
       </c>
     </row>
@@ -483,64 +513,94 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.010078125</v>
+        <v>0.06265560198625031</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0103781138300293</v>
+        <v>0.0640630143510323</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01067583231991007</v>
+        <v>0.06545589704940044</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01097129285645482</v>
+        <v>0.0668343551784569</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01126450776696979</v>
+        <v>0.06819849317017941</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01155548931952197</v>
+        <v>0.06954841479534336</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01184424972320493</v>
+        <v>0.07088422316742155</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01213080112840355</v>
+        <v>0.07220602074646224</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0124151556270576</v>
+        <v>0.07351390934294517</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01269732525292417</v>
+        <v>0.07480799012161557</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01297732198183901</v>
+        <v>0.07608836360529703</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01325515773197666</v>
+        <v>0.07735512967868244</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01353084436410956</v>
+        <v>0.07860838759210352</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01380439368186604</v>
+        <v>0.07984823596527925</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01407581743198707</v>
+        <v>0.08107477279104301</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01434512730458208</v>
+        <v>0.08228809543904875</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01461233493338358</v>
+        <v>0.08348830065945584</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01487745189600065</v>
+        <v>0.08467548458659369</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01514048971417146</v>
+        <v>0.08584974274260518</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0154014598540146</v>
+        <v>0.08701117004106948</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.08815986079060474</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.08929590869845018</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.09041940687402769</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.09153044783248357</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.09262912349821027</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.09371552520834804</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.0947897437162664</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.09585186919502682</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.09690199124082469</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.09794019887641275</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +608,94 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.010078125</v>
+        <v>0.06265560198625031</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0103781138300293</v>
+        <v>0.0640630143510323</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01067583231991007</v>
+        <v>0.06545589704940044</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01097129285645482</v>
+        <v>0.0668343551784569</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01126450776696979</v>
+        <v>0.06819849317017941</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01155548931952197</v>
+        <v>0.06954841479534336</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01184424972320493</v>
+        <v>0.07088422316742155</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01213080112840355</v>
+        <v>0.07220602074646224</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0124151556270576</v>
+        <v>0.07351390934294517</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01269732525292417</v>
+        <v>0.07480799012161557</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01297732198183901</v>
+        <v>0.07608836360529703</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01325515773197666</v>
+        <v>0.07735512967868244</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01353084436410956</v>
+        <v>0.07860838759210352</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01380439368186604</v>
+        <v>0.07984823596527925</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01407581743198707</v>
+        <v>0.08107477279104301</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01434512730458208</v>
+        <v>0.08228809543904875</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01461233493338358</v>
+        <v>0.08348830065945584</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01487745189600065</v>
+        <v>0.08467548458659369</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01514048971417146</v>
+        <v>0.08584974274260518</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0154014598540146</v>
+        <v>0.08701117004106948</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.08815986079060474</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.08929590869845018</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.09041940687402769</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.09153044783248357</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.09262912349821027</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.09371552520834804</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.0947897437162664</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.09585186919502682</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.09690199124082469</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.09794019887641275</v>
       </c>
     </row>
   </sheetData>
